--- a/exp.xlsx
+++ b/exp.xlsx
@@ -472,7 +472,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>4444</v>
       </c>
       <c r="H3">
         <v>18000</v>

--- a/exp.xlsx
+++ b/exp.xlsx
@@ -472,7 +472,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>4444</v>
+        <v>5555</v>
       </c>
       <c r="H3">
         <v>18000</v>

--- a/exp.xlsx
+++ b/exp.xlsx
@@ -517,7 +517,7 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>6666</v>
       </c>
       <c r="H4">
         <v>0</v>

--- a/exp.xlsx
+++ b/exp.xlsx
@@ -771,7 +771,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="J11">
         <v>0</v>

--- a/exp.xlsx
+++ b/exp.xlsx
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I11">
         <v>800</v>

--- a/exp.xlsx
+++ b/exp.xlsx
@@ -559,7 +559,7 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -1788,7 +1788,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>{"version":1,"title":"לוח תקציב שנתי","incomeCats":[{"key":"משכורת_אילן","label":"משכורת אילן","transferDay":1},{"key":"משכורת_גלי","label":"משכורת גלי","transferDay":10},{"key":"מענקים_בונוסים","label":"מענקים\\בונוסים","transferDay":1}],"parentCats":[{"key":"home","label":"בית"},{"key":"insurance","label":"ביטוח"},{"key":"car","label":"רכב"},{"key":"food","label":"מזון"},{"key":"leisure","label":"בילויים"},{"key":"vacations","label":"חופשות"},{"key":"general","label":"כללי"}],"expenseCats":[{"key":"water","label":"מים","parent":"general"},{"key":"property_tax","label":"ארנונה","parent":"general"},{"key":"electricity","label":"חשמל","parent":"general"},{"key":"tv","label":"טלוויזיה","parent":"general"},{"key":"phones","label":"טלפונים","parent":"general"},{"key":"health_fund","label":"קופת חולים","parent":"general"},{"key":"home_insurance","label":"ביטוח דירה","parent":"general"},{"key":"car_insurance","label":"ביטוח רכב","parent":"general"},{"key":"life_insurance","label":"ביטוח חיים","parent":"general"},{"key":"illness_insurance","label":"ביטוח מחלות","parent":"general"},{"key":"cc_visa","label":"אשראי - ויזה הבינלאומי","parent":"general"},{"key":"cc_max","label":"אשראי - מקס הייטק זון","parent":"general"},{"key":"cc_isracard","label":"אשראי - ישראכרט הוט","parent":"general"},{"key":"cc_leumi","label":"אשראי - לאומי","parent":"general"},{"key":"bit_apps","label":"ביט / אפליקציות תשלום","parent":"general"},{"key":"savings","label":"הפרשות וחיסכון","parent":"general"},{"key":"groceries","label":"קניות לבית / סופר","parent":"general"},{"key":"restaurants","label":"מסעדות","parent":"general"},{"key":"shopping_misc","label":"קניות (בלת\"מים)","parent":"general"},{"key":"education","label":"חינוך","parent":"general"},{"key":"clubs","label":"חוגים","parent":"general"}],"period":{"start":5,"end":7},"theme":{"income":"#4a7ba3","expense":"#c17a4e"},"background":"#f9f9f7"}</v>
+        <v>{"version":1,"title":"לוח תקציב שנתי","incomeCats":[{"key":"משכורת_אילן","label":"משכורת אילן","transferDay":1},{"key":"משכורת_גלי","label":"משכורת גלי","transferDay":10},{"key":"מענקים_בונוסים","label":"מענקים\\בונוסים","transferDay":1}],"parentCats":[{"key":"home","label":"בית"},{"key":"insurance","label":"ביטוח"},{"key":"car","label":"רכב"},{"key":"food","label":"מזון"},{"key":"leisure","label":"בילויים"},{"key":"vacations","label":"חופשות"},{"key":"general","label":"כללי"}],"expenseCats":[{"key":"water","label":"מים","parent":"general"},{"key":"property_tax","label":"ארנונה","parent":"general"},{"key":"electricity","label":"חשמל","parent":"general"},{"key":"tv","label":"טלוויזיה","parent":"general"},{"key":"phones","label":"טלפונים","parent":"general"},{"key":"health_fund","label":"קופת חולים","parent":"general"},{"key":"home_insurance","label":"ביטוח דירה","parent":"general"},{"key":"car_insurance","label":"ביטוח רכב","parent":"general"},{"key":"life_insurance","label":"ביטוח חיים","parent":"general"},{"key":"illness_insurance","label":"ביטוח מחלות","parent":"general"},{"key":"cc_visa","label":"אשראי - ויזה הבינלאומי","parent":"general"},{"key":"cc_max","label":"אשראי - מקס הייטק זון","parent":"general"},{"key":"cc_isracard","label":"אשראי - ישראכרט הוט","parent":"general"},{"key":"cc_leumi","label":"אשראי - לאומי","parent":"general"},{"key":"bit_apps","label":"ביט / אפליקציות תשלום","parent":"general"},{"key":"savings","label":"הפרשות וחיסכון","parent":"general"},{"key":"groceries","label":"קניות לבית / סופר","parent":"general"},{"key":"restaurants","label":"מסעדות","parent":"general"},{"key":"shopping_misc","label":"קניות (בלת\"מים)","parent":"general"},{"key":"education","label":"חינוך","parent":"general"},{"key":"clubs","label":"חוגים","parent":"general"}],"period":{"start":4,"end":6},"theme":{"income":"#4a7ba3","expense":"#c17a4e"},"background":"#f9f9f7"}</v>
       </c>
     </row>
   </sheetData>

--- a/exp.xlsx
+++ b/exp.xlsx
@@ -562,7 +562,7 @@
         <v>20000</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H5">
         <v>0</v>

--- a/exp.xlsx
+++ b/exp.xlsx
@@ -517,10 +517,10 @@
         <v>0</v>
       </c>
       <c r="G4">
-        <v>6666</v>
+        <v>12000</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>12000</v>
       </c>
       <c r="I4">
         <v>12000</v>
@@ -1788,7 +1788,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>{"version":1,"title":"לוח תקציב שנתי","incomeCats":[{"key":"משכורת_אילן","label":"משכורת אילן","transferDay":1},{"key":"משכורת_גלי","label":"משכורת גלי","transferDay":10},{"key":"מענקים_בונוסים","label":"מענקים\\בונוסים","transferDay":1}],"parentCats":[{"key":"home","label":"בית"},{"key":"insurance","label":"ביטוח"},{"key":"car","label":"רכב"},{"key":"food","label":"מזון"},{"key":"leisure","label":"בילויים"},{"key":"vacations","label":"חופשות"},{"key":"general","label":"כללי"}],"expenseCats":[{"key":"water","label":"מים","parent":"general"},{"key":"property_tax","label":"ארנונה","parent":"general"},{"key":"electricity","label":"חשמל","parent":"general"},{"key":"tv","label":"טלוויזיה","parent":"general"},{"key":"phones","label":"טלפונים","parent":"general"},{"key":"health_fund","label":"קופת חולים","parent":"general"},{"key":"home_insurance","label":"ביטוח דירה","parent":"general"},{"key":"car_insurance","label":"ביטוח רכב","parent":"general"},{"key":"life_insurance","label":"ביטוח חיים","parent":"general"},{"key":"illness_insurance","label":"ביטוח מחלות","parent":"general"},{"key":"cc_visa","label":"אשראי - ויזה הבינלאומי","parent":"general"},{"key":"cc_max","label":"אשראי - מקס הייטק זון","parent":"general"},{"key":"cc_isracard","label":"אשראי - ישראכרט הוט","parent":"general"},{"key":"cc_leumi","label":"אשראי - לאומי","parent":"general"},{"key":"bit_apps","label":"ביט / אפליקציות תשלום","parent":"general"},{"key":"savings","label":"הפרשות וחיסכון","parent":"general"},{"key":"groceries","label":"קניות לבית / סופר","parent":"general"},{"key":"restaurants","label":"מסעדות","parent":"general"},{"key":"shopping_misc","label":"קניות (בלת\"מים)","parent":"general"},{"key":"education","label":"חינוך","parent":"general"},{"key":"clubs","label":"חוגים","parent":"general"}],"period":{"start":4,"end":6},"theme":{"income":"#4a7ba3","expense":"#c17a4e"},"background":"#f9f9f7"}</v>
+        <v>{"version":1,"title":"לוח תקציב שנתי","incomeCats":[{"key":"משכורת_אילן","label":"משכורת אילן","transferDay":1},{"key":"משכורת_גלי","label":"משכורת גלי","transferDay":10},{"key":"מענקים_בונוסים","label":"מענקים\\בונוסים","transferDay":1}],"parentCats":[{"key":"home","label":"בית"},{"key":"insurance","label":"ביטוח"},{"key":"car","label":"רכב"},{"key":"food","label":"מזון"},{"key":"leisure","label":"בילויים"},{"key":"vacations","label":"חופשות"},{"key":"general","label":"כללי"}],"expenseCats":[{"key":"water","label":"מים","parent":"general"},{"key":"property_tax","label":"ארנונה","parent":"general"},{"key":"electricity","label":"חשמל","parent":"general"},{"key":"tv","label":"טלוויזיה","parent":"general"},{"key":"phones","label":"טלפונים","parent":"general"},{"key":"health_fund","label":"קופת חולים","parent":"general"},{"key":"home_insurance","label":"ביטוח דירה","parent":"general"},{"key":"car_insurance","label":"ביטוח רכב","parent":"general"},{"key":"life_insurance","label":"ביטוח חיים","parent":"general"},{"key":"illness_insurance","label":"ביטוח מחלות","parent":"general"},{"key":"cc_visa","label":"אשראי - ויזה הבינלאומי","parent":"general"},{"key":"cc_max","label":"אשראי - מקס הייטק זון","parent":"general"},{"key":"cc_isracard","label":"אשראי - ישראכרט הוט","parent":"general"},{"key":"cc_leumi","label":"אשראי - לאומי","parent":"general"},{"key":"bit_apps","label":"ביט / אפליקציות תשלום","parent":"general"},{"key":"savings","label":"הפרשות וחיסכון","parent":"general"},{"key":"groceries","label":"קניות לבית / סופר","parent":"general"},{"key":"restaurants","label":"מסעדות","parent":"general"},{"key":"shopping_misc","label":"קניות (בלת\"מים)","parent":"general"},{"key":"education","label":"חינוך","parent":"general"},{"key":"clubs","label":"חוגים","parent":"general"}],"period":{"start":5,"end":7},"theme":{"income":"#4a7ba3","expense":"#c17a4e"},"background":"#f9f9f7"}</v>
       </c>
     </row>
   </sheetData>

--- a/exp.xlsx
+++ b/exp.xlsx
@@ -559,10 +559,10 @@
         <v>0</v>
       </c>
       <c r="F5">
-        <v>20000</v>
+        <v>0</v>
       </c>
       <c r="G5">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -1788,7 +1788,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>{"version":1,"title":"לוח תקציב שנתי","incomeCats":[{"key":"משכורת_אילן","label":"משכורת אילן","transferDay":1},{"key":"משכורת_גלי","label":"משכורת גלי","transferDay":10},{"key":"מענקים_בונוסים","label":"מענקים\\בונוסים","transferDay":1}],"parentCats":[{"key":"home","label":"בית"},{"key":"insurance","label":"ביטוח"},{"key":"car","label":"רכב"},{"key":"food","label":"מזון"},{"key":"leisure","label":"בילויים"},{"key":"vacations","label":"חופשות"},{"key":"general","label":"כללי"}],"expenseCats":[{"key":"water","label":"מים","parent":"general"},{"key":"property_tax","label":"ארנונה","parent":"general"},{"key":"electricity","label":"חשמל","parent":"general"},{"key":"tv","label":"טלוויזיה","parent":"general"},{"key":"phones","label":"טלפונים","parent":"general"},{"key":"health_fund","label":"קופת חולים","parent":"general"},{"key":"home_insurance","label":"ביטוח דירה","parent":"general"},{"key":"car_insurance","label":"ביטוח רכב","parent":"general"},{"key":"life_insurance","label":"ביטוח חיים","parent":"general"},{"key":"illness_insurance","label":"ביטוח מחלות","parent":"general"},{"key":"cc_visa","label":"אשראי - ויזה הבינלאומי","parent":"general"},{"key":"cc_max","label":"אשראי - מקס הייטק זון","parent":"general"},{"key":"cc_isracard","label":"אשראי - ישראכרט הוט","parent":"general"},{"key":"cc_leumi","label":"אשראי - לאומי","parent":"general"},{"key":"bit_apps","label":"ביט / אפליקציות תשלום","parent":"general"},{"key":"savings","label":"הפרשות וחיסכון","parent":"general"},{"key":"groceries","label":"קניות לבית / סופר","parent":"general"},{"key":"restaurants","label":"מסעדות","parent":"general"},{"key":"shopping_misc","label":"קניות (בלת\"מים)","parent":"general"},{"key":"education","label":"חינוך","parent":"general"},{"key":"clubs","label":"חוגים","parent":"general"}],"period":{"start":5,"end":7},"theme":{"income":"#4a7ba3","expense":"#c17a4e"},"background":"#f9f9f7"}</v>
+        <v>{"version":1,"title":"לוח תקציב שנתי","incomeCats":[{"key":"משכורת_אילן","label":"משכורת אילן","transferDay":1},{"key":"משכורת_גלי","label":"משכורת גלי","transferDay":10},{"key":"מענקים_בונוסים","label":"מענקים\\בונוסים","transferDay":1}],"parentCats":[{"key":"home","label":"בית"},{"key":"insurance","label":"ביטוח"},{"key":"car","label":"רכב"},{"key":"food","label":"מזון"},{"key":"leisure","label":"בילויים"},{"key":"vacations","label":"חופשות"},{"key":"general","label":"כללי"}],"expenseCats":[{"key":"water","label":"מים","parent":"general"},{"key":"property_tax","label":"ארנונה","parent":"general"},{"key":"electricity","label":"חשמל","parent":"general"},{"key":"tv","label":"טלוויזיה","parent":"general"},{"key":"phones","label":"טלפונים","parent":"general"},{"key":"health_fund","label":"קופת חולים","parent":"general"},{"key":"home_insurance","label":"ביטוח דירה","parent":"general"},{"key":"car_insurance","label":"ביטוח רכב","parent":"general"},{"key":"life_insurance","label":"ביטוח חיים","parent":"general"},{"key":"illness_insurance","label":"ביטוח מחלות","parent":"general"},{"key":"cc_visa","label":"אשראי - ויזה הבינלאומי","parent":"general"},{"key":"cc_max","label":"אשראי - מקס הייטק זון","parent":"general"},{"key":"cc_isracard","label":"אשראי - ישראכרט הוט","parent":"general"},{"key":"cc_leumi","label":"אשראי - לאומי","parent":"general"},{"key":"bit_apps","label":"ביט / אפליקציות תשלום","parent":"general"},{"key":"savings","label":"הפרשות וחיסכון","parent":"general"},{"key":"groceries","label":"קניות לבית / סופר","parent":"general"},{"key":"restaurants","label":"מסעדות","parent":"general"},{"key":"shopping_misc","label":"קניות (בלת\"מים)","parent":"general"},{"key":"education","label":"חינוך","parent":"general"},{"key":"clubs","label":"חוגים","parent":"general"}],"period":{"start":0,"end":11},"theme":{"income":"#4a7ba3","expense":"#c17a4e"},"background":"#f9f9f7"}</v>
       </c>
     </row>
   </sheetData>

--- a/exp.xlsx
+++ b/exp.xlsx
@@ -675,7 +675,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>500</v>
+        <v>380</v>
       </c>
       <c r="J9">
         <v>0</v>
@@ -771,7 +771,7 @@
         <v>800</v>
       </c>
       <c r="I11">
-        <v>800</v>
+        <v>860</v>
       </c>
       <c r="J11">
         <v>0</v>
@@ -798,40 +798,40 @@
         <v>טלוויזיה</v>
       </c>
       <c r="B12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="N12">
         <f>SUM(B12:M12)</f>
@@ -867,10 +867,10 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="J13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K13">
         <v>0</v>
@@ -963,7 +963,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>192</v>
       </c>
       <c r="J15">
         <v>0</v>
@@ -990,40 +990,40 @@
         <v>ביטוח רכב</v>
       </c>
       <c r="B16">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="F16">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="G16">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="H16">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M16">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="N16">
         <f>SUM(B16:M16)</f>
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>130</v>
       </c>
       <c r="J17">
         <v>0</v>

--- a/exp.xlsx
+++ b/exp.xlsx
@@ -1038,40 +1038,40 @@
         <v>ביטוח חיים</v>
       </c>
       <c r="B17">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="C17">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="D17">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="F17">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="H17">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="I17">
-        <v>130</v>
+        <v>290</v>
       </c>
       <c r="J17">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="L17">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>160</v>
       </c>
       <c r="N17">
         <f>SUM(B17:M17)</f>

--- a/exp.xlsx
+++ b/exp.xlsx
@@ -942,40 +942,40 @@
         <v>ביטוח דירה</v>
       </c>
       <c r="B15">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="F15">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="G15">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="H15">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="I15">
-        <v>192</v>
+        <v>383</v>
       </c>
       <c r="J15">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="L15">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="M15">
-        <v>0</v>
+        <v>191</v>
       </c>
       <c r="N15">
         <f>SUM(B15:M15)</f>
@@ -987,43 +987,43 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>ביטוח רכב</v>
+        <v>רכב כללי</v>
       </c>
       <c r="B16">
-        <v>600</v>
+        <v>725</v>
       </c>
       <c r="C16">
-        <v>600</v>
+        <v>725</v>
       </c>
       <c r="D16">
-        <v>600</v>
+        <v>725</v>
       </c>
       <c r="E16">
-        <v>600</v>
+        <v>725</v>
       </c>
       <c r="F16">
-        <v>600</v>
+        <v>725</v>
       </c>
       <c r="G16">
-        <v>600</v>
+        <v>725</v>
       </c>
       <c r="H16">
-        <v>600</v>
+        <v>725</v>
       </c>
       <c r="I16">
-        <v>600</v>
+        <v>725</v>
       </c>
       <c r="J16">
-        <v>600</v>
+        <v>725</v>
       </c>
       <c r="K16">
-        <v>600</v>
+        <v>725</v>
       </c>
       <c r="L16">
-        <v>600</v>
+        <v>725</v>
       </c>
       <c r="M16">
-        <v>600</v>
+        <v>725</v>
       </c>
       <c r="N16">
         <f>SUM(B16:M16)</f>
@@ -1788,7 +1788,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>{"version":1,"title":"לוח תקציב שנתי","incomeCats":[{"key":"משכורת_אילן","label":"משכורת אילן","transferDay":1},{"key":"משכורת_גלי","label":"משכורת גלי","transferDay":10},{"key":"מענקים_בונוסים","label":"מענקים\\בונוסים","transferDay":1}],"parentCats":[{"key":"home","label":"בית"},{"key":"insurance","label":"ביטוח"},{"key":"car","label":"רכב"},{"key":"food","label":"מזון"},{"key":"leisure","label":"בילויים"},{"key":"vacations","label":"חופשות"},{"key":"general","label":"כללי"}],"expenseCats":[{"key":"water","label":"מים","parent":"general"},{"key":"property_tax","label":"ארנונה","parent":"general"},{"key":"electricity","label":"חשמל","parent":"general"},{"key":"tv","label":"טלוויזיה","parent":"general"},{"key":"phones","label":"טלפונים","parent":"general"},{"key":"health_fund","label":"קופת חולים","parent":"general"},{"key":"home_insurance","label":"ביטוח דירה","parent":"general"},{"key":"car_insurance","label":"ביטוח רכב","parent":"general"},{"key":"life_insurance","label":"ביטוח חיים","parent":"general"},{"key":"illness_insurance","label":"ביטוח מחלות","parent":"general"},{"key":"cc_visa","label":"אשראי - ויזה הבינלאומי","parent":"general"},{"key":"cc_max","label":"אשראי - מקס הייטק זון","parent":"general"},{"key":"cc_isracard","label":"אשראי - ישראכרט הוט","parent":"general"},{"key":"cc_leumi","label":"אשראי - לאומי","parent":"general"},{"key":"bit_apps","label":"ביט / אפליקציות תשלום","parent":"general"},{"key":"savings","label":"הפרשות וחיסכון","parent":"general"},{"key":"groceries","label":"קניות לבית / סופר","parent":"general"},{"key":"restaurants","label":"מסעדות","parent":"general"},{"key":"shopping_misc","label":"קניות (בלת\"מים)","parent":"general"},{"key":"education","label":"חינוך","parent":"general"},{"key":"clubs","label":"חוגים","parent":"general"}],"period":{"start":0,"end":11},"theme":{"income":"#4a7ba3","expense":"#c17a4e"},"background":"#f9f9f7"}</v>
+        <v>{"version":1,"title":"לוח תקציב שנתי","incomeCats":[{"key":"משכורת_אילן","label":"משכורת אילן","transferDay":1},{"key":"משכורת_גלי","label":"משכורת גלי","transferDay":10},{"key":"מענקים_בונוסים","label":"מענקים\\בונוסים","transferDay":1}],"parentCats":[{"key":"home","label":"בית"},{"key":"insurance","label":"ביטוח"},{"key":"car","label":"רכב"},{"key":"food","label":"מזון"},{"key":"leisure","label":"בילויים"},{"key":"vacations","label":"חופשות"},{"key":"general","label":"כללי"}],"expenseCats":[{"key":"water","label":"מים","parent":"general"},{"key":"property_tax","label":"ארנונה","parent":"general"},{"key":"electricity","label":"חשמל","parent":"general"},{"key":"tv","label":"טלוויזיה","parent":"general"},{"key":"phones","label":"טלפונים","parent":"general"},{"key":"health_fund","label":"קופת חולים","parent":"general"},{"key":"home_insurance","label":"ביטוח דירה","parent":"general"},{"key":"car_insurance","label":"רכב כללי","parent":"general"},{"key":"life_insurance","label":"ביטוח חיים","parent":"general"},{"key":"illness_insurance","label":"ביטוח מחלות","parent":"general"},{"key":"cc_visa","label":"אשראי - ויזה הבינלאומי","parent":"general"},{"key":"cc_max","label":"אשראי - מקס הייטק זון","parent":"general"},{"key":"cc_isracard","label":"אשראי - ישראכרט הוט","parent":"general"},{"key":"cc_leumi","label":"אשראי - לאומי","parent":"general"},{"key":"bit_apps","label":"ביט / אפליקציות תשלום","parent":"general"},{"key":"savings","label":"הפרשות וחיסכון","parent":"general"},{"key":"groceries","label":"קניות לבית / סופר","parent":"general"},{"key":"restaurants","label":"מסעדות","parent":"general"},{"key":"shopping_misc","label":"קניות (בלת\"מים)","parent":"general"},{"key":"education","label":"חינוך","parent":"general"},{"key":"clubs","label":"חוגים","parent":"general"}],"period":{"start":0,"end":11},"theme":{"income":"#4a7ba3","expense":"#c17a4e"},"background":"#f9f9f7"}</v>
       </c>
     </row>
   </sheetData>

--- a/exp.xlsx
+++ b/exp.xlsx
@@ -472,7 +472,7 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>5555</v>
+        <v>18000</v>
       </c>
       <c r="H3">
         <v>18000</v>

--- a/exp.xlsx
+++ b/exp.xlsx
@@ -918,7 +918,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0</v>
+        <v>680</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1110,7 +1110,7 @@
         <v>0</v>
       </c>
       <c r="J18">
-        <v>0</v>
+        <v>380</v>
       </c>
       <c r="K18">
         <v>0</v>

--- a/exp.xlsx
+++ b/exp.xlsx
@@ -915,7 +915,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>680</v>
       </c>
       <c r="J14">
         <v>680</v>

--- a/exp.xlsx
+++ b/exp.xlsx
@@ -1788,7 +1788,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>{"version":1,"title":"לוח תקציב שנתי","incomeCats":[{"key":"משכורת_אילן","label":"משכורת אילן","transferDay":1},{"key":"משכורת_גלי","label":"משכורת גלי","transferDay":10},{"key":"מענקים_בונוסים","label":"מענקים\\בונוסים","transferDay":1}],"parentCats":[{"key":"home","label":"בית"},{"key":"insurance","label":"ביטוח"},{"key":"car","label":"רכב"},{"key":"food","label":"מזון"},{"key":"leisure","label":"בילויים"},{"key":"vacations","label":"חופשות"},{"key":"general","label":"כללי"}],"expenseCats":[{"key":"water","label":"מים","parent":"general"},{"key":"property_tax","label":"ארנונה","parent":"general"},{"key":"electricity","label":"חשמל","parent":"general"},{"key":"tv","label":"טלוויזיה","parent":"general"},{"key":"phones","label":"טלפונים","parent":"general"},{"key":"health_fund","label":"קופת חולים","parent":"general"},{"key":"home_insurance","label":"ביטוח דירה","parent":"general"},{"key":"car_insurance","label":"רכב כללי","parent":"general"},{"key":"life_insurance","label":"ביטוח חיים","parent":"general"},{"key":"illness_insurance","label":"ביטוח מחלות","parent":"general"},{"key":"cc_visa","label":"אשראי - ויזה הבינלאומי","parent":"general"},{"key":"cc_max","label":"אשראי - מקס הייטק זון","parent":"general"},{"key":"cc_isracard","label":"אשראי - ישראכרט הוט","parent":"general"},{"key":"cc_leumi","label":"אשראי - לאומי","parent":"general"},{"key":"bit_apps","label":"ביט / אפליקציות תשלום","parent":"general"},{"key":"savings","label":"הפרשות וחיסכון","parent":"general"},{"key":"groceries","label":"קניות לבית / סופר","parent":"general"},{"key":"restaurants","label":"מסעדות","parent":"general"},{"key":"shopping_misc","label":"קניות (בלת\"מים)","parent":"general"},{"key":"education","label":"חינוך","parent":"general"},{"key":"clubs","label":"חוגים","parent":"general"}],"period":{"start":0,"end":11},"theme":{"income":"#4a7ba3","expense":"#c17a4e"},"background":"#f9f9f7"}</v>
+        <v>{"version":1,"title":"לוח תקציב שנתי","incomeCats":[{"key":"משכורת_אילן","label":"משכורת אילן","transferDay":1},{"key":"משכורת_גלי","label":"משכורת גלי","transferDay":10},{"key":"מענקים_בונוסים","label":"מענקים\\בונוסים","transferDay":1}],"parentCats":[{"key":"home","label":"בית"},{"key":"insurance","label":"ביטוח"},{"key":"car","label":"רכב"},{"key":"food","label":"מזון"},{"key":"leisure","label":"בילויים"},{"key":"vacations","label":"חופשות"},{"key":"general","label":"כללי"}],"expenseCats":[{"key":"water","label":"מים","parent":"general"},{"key":"property_tax","label":"ארנונה","parent":"general"},{"key":"electricity","label":"חשמל","parent":"general"},{"key":"tv","label":"טלוויזיה","parent":"general"},{"key":"phones","label":"טלפונים","parent":"general"},{"key":"health_fund","label":"קופת חולים","parent":"general"},{"key":"home_insurance","label":"ביטוח דירה","parent":"general"},{"key":"car_insurance","label":"רכב כללי","parent":"general"},{"key":"life_insurance","label":"ביטוח חיים","parent":"general"},{"key":"illness_insurance","label":"ביטוח מחלות","parent":"general"},{"key":"cc_visa","label":"אשראי - ויזה הבינלאומי","parent":"general"},{"key":"cc_max","label":"אשראי - מקס הייטק זון","parent":"general"},{"key":"cc_isracard","label":"אשראי - ישראכרט הוט","parent":"general"},{"key":"cc_leumi","label":"אשראי - לאומי","parent":"general"},{"key":"bit_apps","label":"ביט / אפליקציות תשלום","parent":"general"},{"key":"savings","label":"הפרשות וחיסכון","parent":"general"},{"key":"groceries","label":"קניות לבית / סופר","parent":"general"},{"key":"restaurants","label":"מסעדות","parent":"general"},{"key":"shopping_misc","label":"קניות (בלת\"מים)","parent":"general"},{"key":"education","label":"חינוך","parent":"general"},{"key":"clubs","label":"חוגים","parent":"general"}],"period":{"start":7,"end":7},"theme":{"income":"#4a7ba3","expense":"#c17a4e"},"background":"#f9f9f7"}</v>
       </c>
     </row>
   </sheetData>
